--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2023_magallanes.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2023_magallanes.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:39</t>
+    <t xml:space="preserve">2026-10-05 02:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -513,7 +513,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>887639.62</v>
+        <v>887639.63</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>837930.75</v>
@@ -604,7 +604,7 @@
         <v>1192651.5</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1236813.12</v>
+        <v>1236813.13</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1220936</v>
